--- a/inv/men.xlsx
+++ b/inv/men.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="37">
   <si>
     <t>titleid</t>
   </si>
   <si>
-    <t>Title</t>
+    <t>title</t>
   </si>
   <si>
     <t>link</t>
@@ -42,18 +42,6 @@
   </si>
   <si>
     <t>men_accessories.jpg</t>
-  </si>
-  <si>
-    <t>men_shoes</t>
-  </si>
-  <si>
-    <t>Men Shoes</t>
-  </si>
-  <si>
-    <t>?page=men_shoes</t>
-  </si>
-  <si>
-    <t>men_shoes.jpg</t>
   </si>
   <si>
     <t>men_bags</t>
@@ -476,7 +464,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="true" style="0"/>
@@ -615,20 +603,6 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
-      </c>
-    </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
